--- a/docs/数据库设计.xlsx
+++ b/docs/数据库设计.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IdeaProjects-MyProjects\spring-cloud-alice\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12615" tabRatio="859"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12615" tabRatio="859"/>
   </bookViews>
   <sheets>
     <sheet name="平台数据表" sheetId="45" r:id="rId1"/>
@@ -14,13 +19,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="97">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -30,6 +36,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">-- </t>
@@ -44,6 +51,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>p</t>
@@ -53,6 +61,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>latform</t>
@@ -62,6 +71,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>_user</t>
@@ -109,6 +119,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>i</t>
@@ -118,6 +129,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>d</t>
@@ -156,6 +168,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">) </t>
@@ -165,6 +178,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>NOT</t>
@@ -174,6 +188,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> NULL COMMENT '</t>
@@ -188,6 +203,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>c</t>
@@ -197,6 +213,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>ompany</t>
@@ -206,6 +223,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>_id</t>
@@ -223,6 +241,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">) NOT NULL </t>
@@ -232,6 +251,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">DEFAULT </t>
@@ -241,6 +261,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>''</t>
@@ -250,6 +271,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> COMMENT '</t>
@@ -312,6 +334,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>)</t>
@@ -321,6 +344,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> NOT NULL </t>
@@ -330,6 +354,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">DEFAULT </t>
@@ -339,6 +364,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1 COMMENT '</t>
@@ -350,6 +376,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>是否启用：</t>
@@ -359,6 +386,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1-启用；0-禁用</t>
@@ -370,6 +398,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>creat</t>
@@ -379,6 +408,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>or</t>
@@ -388,6 +418,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>_</t>
@@ -397,6 +428,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>id</t>
@@ -411,6 +443,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>创建人I</t>
@@ -420,6 +453,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>D</t>
@@ -437,6 +471,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">  NOT NULL DEFAULT </t>
@@ -446,6 +481,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>CURRENT_TIMESTAMP</t>
@@ -455,6 +491,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> COMMENT '</t>
@@ -469,6 +506,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>modifier_</t>
@@ -478,6 +516,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>id</t>
@@ -489,6 +528,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">) DEFAULT </t>
@@ -498,6 +538,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>''</t>
@@ -507,6 +548,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> COMMENT '</t>
@@ -518,6 +560,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>修改人I</t>
@@ -527,6 +570,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>D</t>
@@ -547,6 +591,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">) </t>
@@ -556,6 +601,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">NOT NULL </t>
@@ -565,6 +611,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">DEFAULT </t>
@@ -574,6 +621,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>0 COMMENT '</t>
@@ -597,6 +645,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -606,6 +655,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">   INDEX idx_</t>
@@ -617,6 +667,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>q</t>
@@ -626,6 +677,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="微软雅黑"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>uery</t>
@@ -648,20 +700,218 @@
   </si>
   <si>
     <t>';</t>
+  </si>
+  <si>
+    <t>platform_route</t>
+  </si>
+  <si>
+    <t>platform_route</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>平台路由表</t>
+  </si>
+  <si>
+    <t>平台路由表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>oute_id</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ri</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>predicates</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>filters</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>metadata</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>son</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>路由I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>谓词</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>过滤器</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺序</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> NOT NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT '</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>route_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>`</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    UNIQUE  INDEX idx_</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>route_order</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">) NOT NULL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">DEFAULT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>''</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> COMMENT '</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> NOT NULL DEFAULT 0 COMMENT '</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="General_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="General_)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,171 +923,34 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Geneva"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -858,13 +971,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -876,198 +989,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1090,393 +1017,116 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="52">
+  <cellStyles count="4">
+    <cellStyle name="?_x000c_&quot;_x001b__x000d__x0015_?$_x000b_?_x0007__x0001__x0001_" xfId="2"/>
+    <cellStyle name="百分比 10" xfId="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="百分比 10" xfId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="42" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="43" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="44" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="45" builtinId="47"/>
-    <cellStyle name="?_x000c_&quot;_x001b__x000d__x0015_?$_x000b_?_x0007__x0001__x0001_" xfId="46"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="47" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="48" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="49" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="50" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="51"/>
+    <cellStyle name="常规 2" xfId="3"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="00FF0066"/>
-      <color rgb="00FFCC99"/>
+      <color rgb="FFFF0066"/>
+      <color rgb="FFFFCC99"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1763,13 +1413,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.25" style="3" customWidth="1"/>
@@ -1785,7 +1435,7 @@
     <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
+    <row r="1" spans="1:15" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1799,7 +1449,7 @@
       </c>
       <c r="I1" s="26"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+    <row r="2" spans="1:15" s="1" customFormat="1">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
@@ -1823,7 +1473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
+    <row r="3" spans="1:15" s="1" customFormat="1">
       <c r="A3" s="8"/>
       <c r="B3" s="8" t="s">
         <v>9</v>
@@ -1841,7 +1491,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
+    <row r="4" spans="1:15" s="1" customFormat="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8" t="s">
         <v>12</v>
@@ -1859,7 +1509,7 @@
       </c>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:10">
+    <row r="5" spans="1:15" s="2" customFormat="1">
       <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
@@ -1891,7 +1541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:10">
+    <row r="6" spans="1:15" s="2" customFormat="1">
       <c r="A6" s="14" t="s">
         <v>14</v>
       </c>
@@ -1921,7 +1571,7 @@
       </c>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:10">
+    <row r="7" spans="1:15" s="2" customFormat="1">
       <c r="A7" s="14" t="s">
         <v>14</v>
       </c>
@@ -1951,7 +1601,7 @@
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:10">
+    <row r="8" spans="1:15" s="2" customFormat="1">
       <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
@@ -1981,7 +1631,7 @@
       </c>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" s="2" customFormat="1" spans="1:10">
+    <row r="9" spans="1:15" s="2" customFormat="1">
       <c r="A9" s="14" t="s">
         <v>14</v>
       </c>
@@ -2011,7 +1661,7 @@
       </c>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:15">
+    <row r="10" spans="1:15" s="2" customFormat="1">
       <c r="A10" s="14" t="s">
         <v>14</v>
       </c>
@@ -2045,7 +1695,7 @@
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:15">
+    <row r="11" spans="1:15" s="2" customFormat="1">
       <c r="A11" s="14" t="s">
         <v>14</v>
       </c>
@@ -2079,7 +1729,7 @@
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
     </row>
-    <row r="12" s="2" customFormat="1" spans="1:15">
+    <row r="12" spans="1:15" s="2" customFormat="1">
       <c r="A12" s="14" t="s">
         <v>14</v>
       </c>
@@ -2113,7 +1763,7 @@
       <c r="N12" s="27"/>
       <c r="O12" s="27"/>
     </row>
-    <row r="13" s="2" customFormat="1" spans="1:15">
+    <row r="13" spans="1:15" s="2" customFormat="1">
       <c r="A13" s="14" t="s">
         <v>14</v>
       </c>
@@ -2147,7 +1797,7 @@
       <c r="N13" s="27"/>
       <c r="O13" s="27"/>
     </row>
-    <row r="14" s="2" customFormat="1" spans="1:10">
+    <row r="14" spans="1:15" s="2" customFormat="1">
       <c r="A14" s="14" t="s">
         <v>14</v>
       </c>
@@ -2177,7 +1827,7 @@
       </c>
       <c r="J14" s="14"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
+    <row r="15" spans="1:15" s="2" customFormat="1">
       <c r="A15" s="17" t="s">
         <v>14</v>
       </c>
@@ -2207,7 +1857,7 @@
       </c>
       <c r="J15" s="17"/>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:10">
+    <row r="16" spans="1:15" s="1" customFormat="1">
       <c r="A16" s="17" t="s">
         <v>14</v>
       </c>
@@ -2237,7 +1887,7 @@
       </c>
       <c r="J16" s="17"/>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:10">
+    <row r="17" spans="1:15" s="1" customFormat="1">
       <c r="A17" s="17" t="s">
         <v>14</v>
       </c>
@@ -2263,7 +1913,7 @@
       </c>
       <c r="J17" s="17"/>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:10">
+    <row r="18" spans="1:15" s="1" customFormat="1">
       <c r="A18" s="17" t="s">
         <v>14</v>
       </c>
@@ -2293,7 +1943,7 @@
       </c>
       <c r="J18" s="17"/>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:10">
+    <row r="19" spans="1:15" s="1" customFormat="1">
       <c r="A19" s="17" t="s">
         <v>14</v>
       </c>
@@ -2319,7 +1969,7 @@
       </c>
       <c r="J19" s="17"/>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:15">
+    <row r="20" spans="1:15" s="2" customFormat="1">
       <c r="A20" s="17" t="s">
         <v>14</v>
       </c>
@@ -2353,7 +2003,7 @@
       <c r="N20" s="27"/>
       <c r="O20" s="27"/>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:10">
+    <row r="21" spans="1:15" s="1" customFormat="1">
       <c r="A21" s="11" t="s">
         <v>3</v>
       </c>
@@ -2369,7 +2019,7 @@
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:10">
+    <row r="22" spans="1:15" s="1" customFormat="1">
       <c r="A22" s="11"/>
       <c r="B22" s="11" t="s">
         <v>65</v>
@@ -2387,7 +2037,7 @@
       </c>
       <c r="J22" s="11"/>
     </row>
-    <row r="23" s="2" customFormat="1" spans="1:10">
+    <row r="23" spans="1:15" s="2" customFormat="1">
       <c r="A23" s="22" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2053,7 @@
       <c r="I23" s="22"/>
       <c r="J23" s="22"/>
     </row>
-    <row r="24" s="2" customFormat="1" spans="1:10">
+    <row r="24" spans="1:15" s="2" customFormat="1">
       <c r="A24" s="22"/>
       <c r="B24" s="22" t="s">
         <v>68</v>
@@ -2425,7 +2075,7 @@
       </c>
       <c r="J24" s="22"/>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:10">
+    <row r="25" spans="1:15" s="1" customFormat="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
         <v>73</v>
@@ -2445,11 +2095,565 @@
       </c>
       <c r="J25" s="8"/>
     </row>
-    <row r="26" customFormat="1" ht="13.5"/>
-    <row r="27" customFormat="1" ht="13.5"/>
+    <row r="26" spans="1:15" customFormat="1" ht="13.5"/>
+    <row r="27" spans="1:15" customFormat="1" ht="13.5"/>
+    <row r="28" spans="1:15" s="1" customFormat="1">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="26"/>
+    </row>
+    <row r="29" spans="1:15" s="1" customFormat="1">
+      <c r="A29" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" s="1" customFormat="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:15" s="1" customFormat="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:15" s="2" customFormat="1">
+      <c r="A32" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="12">
+        <v>11</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="2" customFormat="1">
+      <c r="A33" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="15">
+        <v>100</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:15" s="2" customFormat="1">
+      <c r="A34" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="14"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+    </row>
+    <row r="35" spans="1:15" s="2" customFormat="1">
+      <c r="A35" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="27"/>
+    </row>
+    <row r="36" spans="1:15" s="2" customFormat="1">
+      <c r="A36" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="15">
+        <v>200</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:15" s="2" customFormat="1">
+      <c r="A37" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+    </row>
+    <row r="38" spans="1:15" s="2" customFormat="1">
+      <c r="A38" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="H38" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
+    </row>
+    <row r="39" spans="1:15" s="2" customFormat="1">
+      <c r="A39" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="18">
+        <v>1</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="17"/>
+    </row>
+    <row r="40" spans="1:15" s="1" customFormat="1">
+      <c r="A40" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="18">
+        <v>20</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="1:15" s="1" customFormat="1">
+      <c r="A41" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="17"/>
+    </row>
+    <row r="42" spans="1:15" s="1" customFormat="1">
+      <c r="A42" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="18">
+        <v>20</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="17"/>
+    </row>
+    <row r="43" spans="1:15" s="1" customFormat="1">
+      <c r="A43" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="17"/>
+    </row>
+    <row r="44" spans="1:15" s="2" customFormat="1">
+      <c r="A44" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="18">
+        <v>11</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="17"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
+      <c r="O44" s="27"/>
+    </row>
+    <row r="45" spans="1:15" s="1" customFormat="1">
+      <c r="A45" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+    </row>
+    <row r="46" spans="1:15" s="1" customFormat="1">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="11"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J46" s="11"/>
+    </row>
+    <row r="47" spans="1:15" s="2" customFormat="1">
+      <c r="A47" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+    </row>
+    <row r="48" spans="1:15" s="2" customFormat="1">
+      <c r="A48" s="22"/>
+      <c r="B48" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48" s="24"/>
+      <c r="G48" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="H48" s="25"/>
+      <c r="I48" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="J48" s="22"/>
+    </row>
+    <row r="49" spans="1:10" s="1" customFormat="1">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="J49" s="8"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/数据库设计.xlsx
+++ b/docs/数据库设计.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="95">
   <si>
     <r>
       <rPr>
@@ -706,14 +706,14 @@
   </si>
   <si>
     <t>platform_route</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>平台路由表</t>
   </si>
   <si>
     <t>平台路由表</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -729,7 +729,7 @@
       </rPr>
       <t>oute_id</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -745,35 +745,19 @@
       </rPr>
       <t>ri</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>predicates</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>filters</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>metadata</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>j</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>son</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -789,27 +773,88 @@
       </rPr>
       <t>D</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>谓词</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>过滤器</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>元数据</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>顺序</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> NOT NULL</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>route_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>`</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    UNIQUE  INDEX idx_</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>route_order</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">) NOT NULL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">DEFAULT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>''</t>
     </r>
     <r>
       <rPr>
@@ -821,87 +866,11 @@
       </rPr>
       <t xml:space="preserve"> COMMENT '</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>`</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>route_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>`</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    UNIQUE  INDEX idx_</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>route_order</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">) NOT NULL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">DEFAULT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>''</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> COMMENT '</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> NOT NULL DEFAULT 0 COMMENT '</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -909,15 +878,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="General_)"/>
+    <numFmt numFmtId="176" formatCode="General_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1020,90 +996,90 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1175,7 +1151,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1210,7 +1186,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2226,7 +2202,7 @@
         <v>30</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I33" s="14" t="s">
         <v>21</v>
@@ -2243,16 +2219,20 @@
       <c r="C34" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
+      <c r="D34" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="15">
+        <v>200</v>
+      </c>
       <c r="G34" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I34" s="14" t="s">
         <v>21</v>
@@ -2273,16 +2253,20 @@
       <c r="C35" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="15"/>
+      <c r="D35" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="15">
+        <v>200</v>
+      </c>
       <c r="G35" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I35" s="14" t="s">
         <v>21</v>
@@ -2313,7 +2297,7 @@
         <v>200</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H36" s="29" t="s">
         <v>81</v>
@@ -2333,16 +2317,20 @@
       <c r="C37" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="15"/>
+      <c r="D37" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="15">
+        <v>200</v>
+      </c>
       <c r="G37" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I37" s="14" t="s">
         <v>21</v>
@@ -2358,7 +2346,7 @@
         <v>14</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>16</v>
@@ -2369,10 +2357,10 @@
       <c r="E38" s="14"/>
       <c r="F38" s="15"/>
       <c r="G38" s="29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I38" s="14" t="s">
         <v>21</v>
@@ -2612,7 +2600,7 @@
     <row r="48" spans="1:15" s="2" customFormat="1">
       <c r="A48" s="22"/>
       <c r="B48" s="30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C48" s="22"/>
       <c r="D48" s="22" t="s">
@@ -2623,7 +2611,7 @@
       </c>
       <c r="F48" s="24"/>
       <c r="G48" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H48" s="25"/>
       <c r="I48" s="22" t="s">
@@ -2652,7 +2640,7 @@
       <c r="J49" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
